--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,12 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-11-23</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
     <t>2025-11-25</t>
   </si>
   <si>
@@ -287,6 +281,12 @@
   </si>
   <si>
     <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
   </si>
   <si>
     <t>Issue</t>
@@ -367,7 +367,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -378,7 +378,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -466,7 +466,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="12">
@@ -477,7 +477,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="13">
@@ -499,7 +499,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="15">
@@ -510,7 +510,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="16">
@@ -521,7 +521,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="17">
@@ -532,7 +532,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="18">
@@ -543,7 +543,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -554,7 +554,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
@@ -565,7 +565,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -576,7 +576,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="22">
@@ -587,7 +587,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="23">
@@ -598,7 +598,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -620,7 +620,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="26">
@@ -631,7 +631,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -642,7 +642,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="28">
@@ -675,7 +675,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31">
@@ -686,7 +686,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="32">
@@ -697,7 +697,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="33">
@@ -708,7 +708,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="34">
@@ -719,7 +719,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="35">
@@ -730,7 +730,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="36">
@@ -763,7 +763,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="39">
@@ -774,7 +774,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -785,7 +785,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="41">
@@ -796,7 +796,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="42">
@@ -807,7 +807,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="43">
@@ -818,7 +818,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="44">
@@ -873,7 +873,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="49">
@@ -884,7 +884,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="50">
@@ -950,7 +950,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="56">
@@ -961,7 +961,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="57">
@@ -972,7 +972,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="58">
@@ -994,7 +994,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="60">
@@ -1005,7 +1005,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="61">
@@ -1027,7 +1027,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="63">
@@ -1049,7 +1049,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="65">
@@ -1060,7 +1060,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="66">
@@ -1071,7 +1071,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="67">
@@ -1082,7 +1082,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="68">
@@ -1093,7 +1093,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="69">
@@ -1181,7 +1181,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="77">
@@ -1203,7 +1203,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="79">
@@ -1214,7 +1214,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="80">
@@ -1225,7 +1225,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="81">
@@ -1236,7 +1236,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="82">
@@ -1258,7 +1258,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="84">
@@ -1280,7 +1280,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="86">
@@ -1324,7 +1324,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
   <si>
     <t>Date</t>
   </si>
@@ -25,18 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -287,6 +275,15 @@
   </si>
   <si>
     <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t>Issue</t>
@@ -345,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -411,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -422,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="9">
@@ -444,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="10">
@@ -466,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -477,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="13">
@@ -488,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="14">
@@ -499,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="15">
@@ -510,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="16">
@@ -521,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="17">
@@ -532,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="18">
@@ -543,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="19">
@@ -554,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -565,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="21">
@@ -587,7 +584,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -609,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -620,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -631,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -642,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="28">
@@ -675,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -686,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -697,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -708,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -719,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -730,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -763,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>30.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="39">
@@ -774,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="40">
@@ -785,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="41">
@@ -796,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="42">
@@ -829,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="45">
@@ -840,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="46">
@@ -851,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -862,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="48">
@@ -906,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="52">
@@ -917,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="53">
@@ -939,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="55">
@@ -950,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="56">
@@ -961,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="57">
@@ -972,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="58">
@@ -983,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="59">
@@ -1005,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="61">
@@ -1016,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="62">
@@ -1027,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="63">
@@ -1038,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="64">
@@ -1049,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="65">
@@ -1060,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="66">
@@ -1071,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="67">
@@ -1137,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="73">
@@ -1170,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="76">
@@ -1181,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="77">
@@ -1192,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="78">
@@ -1203,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="79">
@@ -1214,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="80">
@@ -1258,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="84">
@@ -1280,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="86">
@@ -1291,7 +1288,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="87">
@@ -1302,7 +1299,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="88">
@@ -1313,17 +1310,6 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
         <v>31.0</v>
       </c>
     </row>
@@ -1339,13 +1325,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1360,13 +1346,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>Issue</t>
@@ -342,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1311,6 +1314,17 @@
       </c>
       <c r="C88" t="n" s="0">
         <v>31.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>32.0</v>
       </c>
     </row>
   </sheetData>
@@ -1325,13 +1339,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1346,13 +1360,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>Issue</t>
@@ -345,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1325,6 +1331,28 @@
       </c>
       <c r="C89" t="n" s="0">
         <v>32.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -1339,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1360,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -23,9 +23,6 @@
   </si>
   <si>
     <t>Valid</t>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -351,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -406,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="7">
@@ -450,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="10">
@@ -472,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="13">
@@ -505,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="15">
@@ -527,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="17">
@@ -549,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="20">
@@ -582,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -626,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="28">
@@ -670,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -714,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="36">
@@ -758,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="38">
@@ -824,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="44">
@@ -901,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="51">
@@ -923,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="57">
@@ -1000,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="61">
@@ -1033,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="63">
@@ -1132,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="73">
@@ -1165,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="76">
@@ -1209,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="80">
@@ -1275,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="85">
@@ -1319,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,17 +1338,6 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>33.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
         <v>33.0</v>
       </c>
     </row>
@@ -1367,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1388,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,12 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
     <t>2025-12-02</t>
   </si>
   <si>
@@ -290,6 +284,12 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
   </si>
   <si>
     <t>Issue</t>
@@ -381,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="6">
@@ -425,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="17">
@@ -546,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -601,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -689,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="37">
@@ -799,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="43">
@@ -876,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="51">
@@ -920,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="54">
@@ -953,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="56">
@@ -975,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="58">
@@ -986,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="62">
@@ -1107,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="70">
@@ -1129,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="72">
@@ -1140,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="75">
@@ -1184,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="77">
@@ -1206,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="79">
@@ -1250,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="84">
@@ -1294,7 +1294,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,7 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -23,9 +23,6 @@
   </si>
   <si>
     <t>Valid</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-03</t>
@@ -348,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -370,7 +367,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +378,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +411,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -436,7 +433,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +444,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -469,7 +466,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="12">
@@ -491,7 +488,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -513,7 +510,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +521,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="17">
@@ -546,7 +543,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="19">
@@ -590,7 +587,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +598,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +609,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -634,7 +631,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -678,7 +675,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +686,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +697,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -722,7 +719,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="35">
@@ -788,7 +785,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="41">
@@ -865,7 +862,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="48">
@@ -887,7 +884,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +895,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +906,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +917,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +928,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="54">
@@ -964,7 +961,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="57">
@@ -975,7 +972,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="58">
@@ -997,7 +994,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="60">
@@ -1096,7 +1093,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1104,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="70">
@@ -1129,7 +1126,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="72">
@@ -1140,7 +1137,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="73">
@@ -1173,7 +1170,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1181,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="77">
@@ -1239,7 +1236,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="82">
@@ -1283,7 +1280,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1291,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="87">
@@ -1316,7 +1313,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,17 +1324,6 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>34.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
         <v>34.0</v>
       </c>
     </row>
@@ -1353,13 +1339,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1360,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -25,9 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
     <t>2025-12-04</t>
   </si>
   <si>
@@ -287,6 +284,12 @@
   </si>
   <si>
     <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
   </si>
   <si>
     <t>Issue</t>
@@ -345,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -367,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="3">
@@ -400,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="6">
@@ -422,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -455,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="13">
@@ -499,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="15">
@@ -510,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="18">
@@ -576,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -587,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="23">
@@ -598,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -620,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -664,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -675,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="31">
@@ -686,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -708,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="34">
@@ -774,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="40">
@@ -851,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="47">
@@ -873,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="49">
@@ -884,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
@@ -895,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="51">
@@ -906,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="52">
@@ -917,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="53">
@@ -950,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="56">
@@ -961,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="57">
@@ -983,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="59">
@@ -1082,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="68">
@@ -1093,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="69">
@@ -1115,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="71">
@@ -1126,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="72">
@@ -1159,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="75">
@@ -1170,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="76">
@@ -1225,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="81">
@@ -1269,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="85">
@@ -1280,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="86">
@@ -1302,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="88">
@@ -1324,7 +1327,18 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>35.0</v>
       </c>
     </row>
   </sheetData>
@@ -1339,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1360,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,12 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
     <t>2025-12-06</t>
   </si>
   <si>
@@ -290,6 +284,12 @@
   </si>
   <si>
     <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
   </si>
   <si>
     <t>Issue</t>
@@ -381,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="21">
@@ -579,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -590,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -645,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="33">
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="39">
@@ -832,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +843,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="46">
@@ -854,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -876,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="50">
@@ -909,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="52">
@@ -931,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="56">
@@ -964,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="57">
@@ -975,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="58">
@@ -1063,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="66">
@@ -1085,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="70">
@@ -1118,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="71">
@@ -1140,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="73">
@@ -1162,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="75">
@@ -1206,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="80">
@@ -1250,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="84">
@@ -1272,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1294,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="90">

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,36 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
     <t>2025-12-16</t>
   </si>
   <si>
@@ -290,6 +260,36 @@
   </si>
   <si>
     <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
   </si>
   <si>
     <t>Issue</t>
@@ -370,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -469,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -491,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="17">
@@ -535,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="18">
@@ -546,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
@@ -579,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="22">
@@ -590,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="39">
@@ -777,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="40">
@@ -788,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="41">
@@ -799,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="43">
@@ -821,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="44">
@@ -832,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +843,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="46">
@@ -854,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="47">
@@ -865,7 +865,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="48">
@@ -876,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="56">
@@ -986,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="63">
@@ -1041,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="64">
@@ -1052,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="70">
@@ -1118,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="71">
@@ -1129,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="72">
@@ -1140,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="75">
@@ -1173,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="77">
@@ -1195,7 +1195,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="78">
@@ -1206,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="80">
@@ -1228,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="81">
@@ -1239,7 +1239,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="82">
@@ -1250,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="84">
@@ -1272,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1294,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,7 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -25,69 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
     <t>2026-01-06</t>
   </si>
   <si>
@@ -290,6 +227,72 @@
   </si>
   <si>
     <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
   </si>
   <si>
     <t>Issue</t>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -370,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>31.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="17">
@@ -535,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>30.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="18">
@@ -546,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="21">
@@ -579,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="22">
@@ -590,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="39">
@@ -777,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="40">
@@ -788,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="41">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>24.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="43">
@@ -821,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="44">
@@ -832,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
@@ -854,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="47">
@@ -865,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="48">
@@ -876,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>27.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="56">
@@ -964,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="57">
@@ -975,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="58">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>29.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="63">
@@ -1041,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -1052,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="68">
@@ -1129,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="72">
@@ -1140,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="75">
@@ -1173,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="77">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="78">
@@ -1206,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="80">
@@ -1228,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="81">
@@ -1239,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="82">
@@ -1250,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="84">
@@ -1272,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,6 +1341,17 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
         <v>31.0</v>
       </c>
     </row>
@@ -1353,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,21 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
     <t>2026-01-11</t>
   </si>
   <si>
@@ -293,6 +278,21 @@
   </si>
   <si>
     <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="6">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="10">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="30">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="38">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="56">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="62">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="73">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="91">

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,45 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
     <t>2026-01-24</t>
   </si>
   <si>
@@ -293,6 +254,45 @@
   </si>
   <si>
     <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="47">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="85">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,81 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
     <t>2026-02-18</t>
   </si>
   <si>
@@ -293,6 +218,81 @@
   </si>
   <si>
     <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>24.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>26.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>34.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>27.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>30.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>32.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>32.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>32.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>31.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>33.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>33.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>35.0</v>
+        <v>45.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,42 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>2026-03-02</t>
   </si>
   <si>
@@ -293,6 +257,42 @@
   </si>
   <si>
     <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="30">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="48">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>32.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>38.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="91">

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,21 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2026-03-07</t>
   </si>
   <si>
@@ -293,6 +278,21 @@
   </si>
   <si>
     <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="18">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="36">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="42">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="45">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="63">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="80">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,30 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-03-07</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
     <t>2026-03-15</t>
   </si>
   <si>
@@ -293,6 +269,30 @@
   </si>
   <si>
     <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="25">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="27">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="37">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="81">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -25,39 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
     <t>2026-03-26</t>
   </si>
   <si>
@@ -293,6 +260,36 @@
   </si>
   <si>
     <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
   </si>
   <si>
     <t>Issue</t>
@@ -351,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -373,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="3">
@@ -395,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="24">
@@ -626,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +843,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +865,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>38.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="70">
@@ -1165,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1195,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>46.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1239,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1294,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>47.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,18 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>49.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
   </sheetData>
@@ -1367,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1388,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -25,21 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
     <t>2026-03-31</t>
   </si>
   <si>
@@ -290,6 +275,24 @@
   </si>
   <si>
     <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
   </si>
   <si>
     <t>Issue</t>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -370,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="12">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="17">
@@ -535,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="18">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -601,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="39">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="43">
@@ -821,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="44">
@@ -832,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="46">
@@ -854,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="47">
@@ -865,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="48">
@@ -876,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="56">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="63">
@@ -1041,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="64">
@@ -1052,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="70">
@@ -1151,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="75">
@@ -1173,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="77">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="78">
@@ -1206,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>47.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1228,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1239,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="82">
@@ -1250,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="84">
@@ -1272,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>54.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,7 +1341,18 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>65.0</v>
       </c>
     </row>
   </sheetData>
@@ -1353,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
     <t>2026-04-06</t>
   </si>
   <si>
@@ -293,6 +275,24 @@
   </si>
   <si>
     <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="15">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="34">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="51">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="65">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="88">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
     <t>2026-04-12</t>
   </si>
   <si>
@@ -293,6 +275,24 @@
   </si>
   <si>
     <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="28">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="45">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="59">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="82">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,30 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
     <t>2026-04-20</t>
   </si>
   <si>
@@ -293,6 +269,30 @@
   </si>
   <si>
     <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
   </si>
   <si>
     <t>Issue</t>
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="45">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="74">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="78">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="80">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
     <t>2026-04-26</t>
   </si>
   <si>
@@ -293,6 +275,24 @@
   </si>
   <si>
     <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="14">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="31">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="45">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="68">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,33 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
     <t>2026-05-05</t>
   </si>
   <si>
@@ -293,6 +266,33 @@
   </si>
   <si>
     <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>37.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="30">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="60">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="66">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>71.0</v>
+        <v>58.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,30 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
     <t>2026-05-13</t>
   </si>
   <si>
@@ -293,6 +269,30 @@
   </si>
   <si>
     <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="22">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="51">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="55">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="57">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="75">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>69.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
     <t>2026-05-19</t>
   </si>
   <si>
@@ -293,6 +275,21 @@
   </si>
   <si>
     <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
   </si>
   <si>
     <t>Issue</t>
@@ -351,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -373,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="8">
@@ -450,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="22">
@@ -615,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="45">
@@ -857,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +865,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1195,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>67.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1239,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="84">
@@ -1341,18 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>57.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
   </sheetData>
@@ -1367,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1388,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
   </si>
   <si>
@@ -290,6 +272,27 @@
   </si>
   <si>
     <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
   </si>
   <si>
     <t>Issue</t>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>48.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="16">
@@ -546,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>48.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="21">
@@ -579,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="22">
@@ -590,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="39">
@@ -788,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="41">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="43">
@@ -821,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="44">
@@ -832,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="46">
@@ -854,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="47">
@@ -865,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="48">
@@ -876,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="49">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="56">
@@ -964,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="57">
@@ -975,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="58">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="63">
@@ -1041,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="64">
@@ -1052,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="70">
@@ -1118,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="71">
@@ -1129,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>67.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="72">
@@ -1140,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="75">
@@ -1173,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="77">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="78">
@@ -1272,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="86">
@@ -1294,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="87">
@@ -1305,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="88">
@@ -1316,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="89">
@@ -1327,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,7 +1341,18 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
@@ -1353,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,33 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -293,6 +266,33 @@
   </si>
   <si>
     <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>Issue</t>
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="37">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>71.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="72">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="89">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,33 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>2026-06-07</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
     <t>2026-06-12</t>
   </si>
   <si>
@@ -293,6 +266,33 @@
   </si>
   <si>
     <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>48.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>47.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>49.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>54.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>60.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="22">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="28">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>71.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="55">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="63">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="80">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1297,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="87">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
